--- a/business_forms/041_price_consistency_clarification_contact_form--business_forms.xlsx
+++ b/business_forms/041_price_consistency_clarification_contact_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1006,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>support_team</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Support Team</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Customer Support</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1209,29 +1209,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>assistance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Assistance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>product_service_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assistance</t>
+          <t>product_service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assistance</t>
+          <t>Product Service</t>
         </is>
       </c>
     </row>
@@ -1243,29 +1243,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>product_service</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Product Service</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>product_service_choices</t>
+          <t>support_service_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>support_service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Support Service</t>
         </is>
       </c>
     </row>
@@ -1277,29 +1277,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>support_service</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Support Service</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>support_service_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1311,29 +1311,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1345,29 +1345,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>services_choices</t>
+          <t>help_desk_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1379,29 +1379,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>help_desk_choices</t>
+          <t>support_team_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1413,29 +1413,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>support_team_choices</t>
+          <t>assistance_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1447,29 +1447,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>assistance_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1481,29 +1481,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>help_choices</t>
+          <t>service_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1515,29 +1515,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>service_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1549,27 +1549,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>help_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
